--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2026.xlsx
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1393093-673-CM26</t>
+          <t>3328-1892-SE26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -595,48 +595,52 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.213.064-5</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>42005.51</v>
+        <v>35501.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>591-86-CM26</t>
+          <t>1393093-673-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +655,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,27 +665,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>METASOFT SOCIEDAD POR ACCIONES</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>76.213.064-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +695,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1718926.68</v>
+        <v>42005.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>584105-167-CM26</t>
+          <t>591-86-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -722,43 +726,47 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>19011.93</v>
+        <v>1718926.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>630760-1-CM26</t>
+          <t>584105-167-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -783,12 +791,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +806,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10603.24</v>
+        <v>19011.93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2273-537-CM26</t>
+          <t>630760-1-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -844,12 +852,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,28 +867,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PAIS DIGITAL SPA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.015.597-5</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10717.53</v>
+        <v>10603.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>701-373-CM26</t>
+          <t>1057414-512-SE26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +907,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,43 +917,47 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ANIDA CONSULTORES S A</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.680.090-2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>87794.46000000001</v>
+        <v>2956.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>711841-228-CM26</t>
+          <t>2273-537-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +972,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +982,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,22 +997,26 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>PAIS DIGITAL SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>77.015.597-5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>18470.68</v>
+        <v>10717.53</v>
       </c>
     </row>
     <row r="10">
@@ -1063,7 +1083,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1314-13-CM26</t>
+          <t>701-373-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1098,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,27 +1108,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>ANIDA CONSULTORES S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>77.680.090-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1138,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>32258.59</v>
+        <v>87794.46000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>45-175-CM26</t>
+          <t>711841-228-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1159,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1169,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,28 +1184,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>365433.57</v>
+        <v>18470.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1016-73-CM26</t>
+          <t>1314-13-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,12 +1234,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,28 +1249,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>30606.2</v>
+        <v>32258.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>606-311-CM26</t>
+          <t>45-175-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1266,17 +1294,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1314,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1329,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>85311.75</v>
+        <v>365433.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1602-88-CM26</t>
+          <t>1016-73-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1350,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,28 +1375,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>KLEINROCK SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.146.212-K</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>30551.13</v>
+        <v>30606.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1602-87-CM26</t>
+          <t>606-311-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1415,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,22 +1440,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>VAB Ingeniería de Software Limitada</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.090.261-6</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>27849.33</v>
+        <v>85311.75</v>
       </c>
     </row>
     <row r="17">
@@ -1477,7 +1513,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1490,7 +1530,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1602-84-CM26</t>
+          <t>1602-88-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1530,22 +1570,26 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VAB Ingeniería de Software Limitada</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.090.261-6</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>77.146.212-K</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>52961.55</v>
+        <v>30551.13</v>
       </c>
     </row>
     <row r="19">
@@ -1599,7 +1643,11 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1612,7 +1660,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1607-76-CM26</t>
+          <t>1602-84-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,37 +1675,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>BINARY BAG</t>
+          <t>VAB Ingeniería de Software Limitada</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.848.560-7</t>
+          <t>76.090.261-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1715,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>752030.39</v>
+        <v>52961.55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>622-302-CM26</t>
+          <t>1602-87-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1736,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1746,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.805.000-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1761,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>VAB Ingeniería de Software Limitada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.090.261-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1776,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>24372.73</v>
+        <v>27849.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1725-703-CM26</t>
+          <t>1607-76-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,37 +1797,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>BINARY BAG</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.848.560-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1837,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7272.5</v>
+        <v>752030.39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2963-39-CM26</t>
+          <t>622-302-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1858,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1868,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.072.400-6</t>
+          <t>60.805.000-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,28 +1883,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>20467.65</v>
+        <v>24372.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>188-539-CM26</t>
+          <t>1725-703-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,53 +1923,57 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7663.01</v>
+        <v>7272.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1067455-75-CM26</t>
+          <t>2963-39-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1988,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1998,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>62.000.420-0</t>
+          <t>69.072.400-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LA GRANJA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +2013,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>APHIX INFORMATICA LIMITADA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.170.582-2</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +2028,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>34106.66</v>
+        <v>20467.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1469-2275-CM26</t>
+          <t>188-539-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +2049,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,27 +2059,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,7 +2089,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>59382.8</v>
+        <v>7663.01</v>
       </c>
     </row>
     <row r="27">
@@ -2100,7 +2156,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4452-736-CM26</t>
+          <t>1067455-75-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,37 +2171,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>62.000.420-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SUBSECRETARIA DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INFO WORLD SA</t>
+          <t>APHIX INFORMATICA LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.532.020-2</t>
+          <t>76.170.582-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2211,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>24725.55</v>
+        <v>34106.66</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1109692-222-CM26</t>
+          <t>1469-2275-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2232,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,43 +2242,47 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.754.348-2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9984.700000000001</v>
+        <v>59382.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1375758-71-CM26</t>
+          <t>1177296-280-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,17 +2302,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2322,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Andestic SpA</t>
+          <t>ZAMBONI INGENIEROS ASOCIADOS SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
+          <t>78.974.330-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2337,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>48357.8</v>
+        <v>8631.93</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4754-7-CM26</t>
+          <t>4452-736-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,32 +2363,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
+          <t>INFO WORLD SA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.198.095-5</t>
+          <t>96.532.020-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2398,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>54240.36</v>
+        <v>24725.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1177296-280-CM26</t>
+          <t>1109692-222-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2364,48 +2424,52 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ZAMBONI INGENIEROS ASOCIADOS SPA</t>
+          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.974.330-4</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>77.754.348-2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8631.93</v>
+        <v>9984.700000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4754-8-CM26</t>
+          <t>1375758-71-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2484,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2494,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2509,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MCL CONSULTING</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.314.701-0</t>
+          <t>76.031.392-0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2524,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>34950.64</v>
+        <v>48357.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1314-15-CM26</t>
+          <t>4754-7-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2545,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2555,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2570,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
+          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.528.848-7</t>
+          <t>76.198.095-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2585,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>102588.74</v>
+        <v>54240.36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>622844-32-CM26</t>
+          <t>1305532-67-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,27 +2616,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
+          <t>NAPSIS SPA.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.198.095-5</t>
+          <t>76.093.358-9</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2646,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>54188.6</v>
+        <v>55513.17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1305532-67-CM26</t>
+          <t>4754-8-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,27 +2677,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NAPSIS SPA.</t>
+          <t>MCL CONSULTING</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.093.358-9</t>
+          <t>76.314.701-0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2707,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>55513.17</v>
+        <v>34950.64</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>699360-62-CM26</t>
+          <t>1314-15-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2728,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2753,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Geosolve Cia Ltda</t>
+          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.562.690-0</t>
+          <t>76.528.848-7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2768,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>30569.47</v>
+        <v>102588.74</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2410-423-CM26</t>
+          <t>622844-32-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2789,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,27 +2799,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>76.198.095-5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2829,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>9704.5</v>
+        <v>54188.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3506-625-CM26</t>
+          <t>2410-423-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,27 +2860,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2890,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7651.56</v>
+        <v>9704.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2345-267-CM26</t>
+          <t>3506-625-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2911,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,43 +2921,47 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>330201.73</v>
+        <v>7651.56</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1005498-123-CM26</t>
+          <t>699360-62-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2976,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +3001,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SPIELUP SPA</t>
+          <t>Geosolve Cia Ltda</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.582.047-2</t>
+          <t>76.562.690-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +3016,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>21311.9</v>
+        <v>30569.47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1191449-89-CM26</t>
+          <t>2345-267-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +3037,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +3047,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.905.006-3</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +3062,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>KDU INGENIERIA LIMITADA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.272.692-0</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3077,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>86591.38</v>
+        <v>330201.73</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3954-31-CM26</t>
+          <t>1005498-123-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3098,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,27 +3108,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.091.500-6</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERALILLO</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>SPIELUP SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>76.582.047-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3138,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>223123.85</v>
+        <v>21311.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5768-123-CM26</t>
+          <t>3954-31-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,43 +3169,47 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.091.500-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>NETICS SPA</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.363.873-1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>30417.15</v>
+        <v>223123.85</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>598-176-CM26</t>
+          <t>5768-123-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3224,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3234,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3249,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>NETICS SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.363.873-1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3264,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>36032.48</v>
+        <v>30417.15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>586-331-CM26</t>
+          <t>1191449-89-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,37 +3285,37 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.905.006-3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>KDU INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>76.272.692-0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3325,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>209143.07</v>
+        <v>86591.38</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1005498-124-CM26</t>
+          <t>586-331-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3284,27 +3356,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3386,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>60231.56</v>
+        <v>209143.07</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1602-95-CM26</t>
+          <t>1005498-124-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3340,17 +3412,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,28 +3432,32 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>17700.24</v>
+        <v>60231.56</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>918434-299-CM26</t>
+          <t>1602-95-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3406,12 +3482,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.980.680-8</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,28 +3497,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Global Catalog Ltda.</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.071.943-9</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>648888</v>
+        <v>17700.24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>948354-1191-CM26</t>
+          <t>918434-299-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3537,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3547,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>61.980.680-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3562,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>Global Catalog Ltda.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.071.943-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3577,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>63899.52</v>
+        <v>648888</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>765-174-CM26</t>
+          <t>598-176-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3598,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,43 +3608,47 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.513.000-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>31171.73</v>
+        <v>36032.48</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1725-773-CM26</t>
+          <t>948354-1191-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3663,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,27 +3673,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3703,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>53626.88</v>
+        <v>63899.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>584105-190-CM26</t>
+          <t>765-174-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3724,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,27 +3734,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,7 +3764,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>33321.71</v>
+        <v>31171.73</v>
       </c>
     </row>
     <row r="54">
@@ -3747,7 +3831,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1068241-5-CM26</t>
+          <t>584105-190-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3787,12 +3871,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.444.489-2</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3886,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8788.35</v>
+        <v>33321.71</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>591-293-CM26</t>
+          <t>1725-773-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,27 +3917,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3947,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>73717.23</v>
+        <v>53626.88</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1602-96-CM26</t>
+          <t>1068241-5-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3894,12 +3978,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3993,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.444.489-2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +4008,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>15657.61</v>
+        <v>8788.35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4555-192-CM26</t>
+          <t>1602-96-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +4029,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,43 +4039,47 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LUUK SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.363.384-3</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>71485.77</v>
+        <v>15657.61</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5251-662-CM26</t>
+          <t>591-293-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4094,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,43 +4104,47 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>31115.02</v>
+        <v>73717.23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3729-93-CM26</t>
+          <t>5872-159-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4072,32 +4164,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.090.300-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>INFO WORLD SA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>96.532.020-2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4199,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>8273.450000000001</v>
+        <v>19719.87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>918434-307-CM26</t>
+          <t>1469-2464-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,27 +4230,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.980.680-8</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>FabricApp SpA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>76.650.494-9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,7 +4260,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>94835.64</v>
+        <v>40142.28</v>
       </c>
     </row>
     <row r="62">
@@ -4222,7 +4314,11 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4235,7 +4331,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1469-2464-CM26</t>
+          <t>4168-1247-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4260,12 +4356,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.130.500-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,28 +4371,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>FabricApp SpA</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.650.494-9</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>40142.28</v>
+        <v>36252.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4168-1247-CM26</t>
+          <t>3729-93-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4321,27 +4421,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>69.090.300-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4451,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>36252.2</v>
+        <v>8273.450000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5872-159-CM26</t>
+          <t>5251-662-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4377,17 +4477,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,28 +4497,32 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>INFO WORLD SA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.532.020-2</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>19719.87</v>
+        <v>31115.02</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>711-383-CM26</t>
+          <t>4555-192-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4537,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,43 +4547,47 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>LUUK SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>77.363.384-3</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>30986.59</v>
+        <v>71485.77</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3553-341-CM26</t>
+          <t>918434-307-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4602,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4612,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>61.980.680-8</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4627,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4642,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>23826.19</v>
+        <v>94835.64</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1725-793-CM26</t>
+          <t>711-383-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4565,43 +4673,47 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.212.000-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>14336.79</v>
+        <v>30986.59</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1591-157-CM26</t>
+          <t>3553-341-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,12 +4738,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,28 +4753,32 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CONCORDIA SPA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.751.321-6</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>52034.2</v>
+        <v>23826.19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>599-140-CM26</t>
+          <t>1725-793-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4687,43 +4803,47 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.213.064-5</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>37874.54</v>
+        <v>14336.79</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1005498-128-CM26</t>
+          <t>1591-157-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,22 +4858,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4883,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>MORRIS Y OPAZO SPA</t>
+          <t>CONCORDIA SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.307.580-k</t>
+          <t>76.751.321-6</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4898,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>73153.99000000001</v>
+        <v>52034.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>756-255-CM26</t>
+          <t>599-140-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4919,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4929,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4944,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
+          <t>METASOFT SOCIEDAD POR ACCIONES</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.092.019-3</t>
+          <t>76.213.064-5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,67 +4959,201 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>15000.28</v>
+        <v>37874.54</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>1005498-128-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>60.810.000-8</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>MORRIS Y OPAZO SPA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.307.580-k</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>73153.99000000001</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>756-255-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>60.701.000-5</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>76.092.019-3</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>15000.28</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>2341-424-CM26</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>69.072.700-5</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
         <is>
           <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="n">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
         <v>34730.82</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2026.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
